--- a/public/abc2/material/comercio-ventas.xlsx
+++ b/public/abc2/material/comercio-ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G85"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,137 +407,1956 @@
         <v>Producto</v>
       </c>
       <c r="C1" t="str">
+        <v>Categoría</v>
+      </c>
+      <c r="D1" t="str">
         <v>Cantidad</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Precio unit.</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Total</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Pago</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>01/07</v>
+        <v>01/07/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>Gaseosa 2.25L</v>
-      </c>
-      <c r="C2">
-        <v>48</v>
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Cervezas</v>
       </c>
       <c r="D2">
-        <v>1800</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>86400</v>
+        <v>2200</v>
+      </c>
+      <c r="F2">
+        <v>26400</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Transferencia</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>01/07</v>
+        <v>01/07/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>Agua 2L</v>
-      </c>
-      <c r="C3">
-        <v>60</v>
+        <v>Cerveza negra 1L</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Cervezas</v>
       </c>
       <c r="D3">
-        <v>900</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>54000</v>
+        <v>2600</v>
+      </c>
+      <c r="F3">
+        <v>46800</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Débito</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>02/07</v>
+        <v>01/07/2026</v>
       </c>
       <c r="B4" t="str">
-        <v>Cerveza rubia 1L</v>
-      </c>
-      <c r="C4">
-        <v>36</v>
+        <v>Vino tinto</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Vinos</v>
       </c>
       <c r="D4">
-        <v>2200</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>79200</v>
+        <v>3500</v>
+      </c>
+      <c r="F4">
+        <v>84000</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Cuenta corriente</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>02/07</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B5" t="str">
-        <v>Vino tinto</v>
-      </c>
-      <c r="C5">
-        <v>24</v>
+        <v>Vino blanco</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Vinos</v>
       </c>
       <c r="D5">
-        <v>3500</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>84000</v>
+        <v>3200</v>
+      </c>
+      <c r="F5">
+        <v>57600</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Débito</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>03/07</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B6" t="str">
         <v>Fernet 750ml</v>
       </c>
-      <c r="C6">
-        <v>18</v>
+      <c r="C6" t="str">
+        <v>Aperitivos</v>
       </c>
       <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
         <v>9500</v>
       </c>
-      <c r="E6">
-        <v>171000</v>
+      <c r="F6">
+        <v>228000</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Cuenta corriente</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>03/07</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B7" t="str">
-        <v>Jugo 1L</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
+        <v>Gin 750ml</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Destilados</v>
       </c>
       <c r="D7">
-        <v>1100</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>44000</v>
+        <v>12000</v>
+      </c>
+      <c r="F7">
+        <v>360000</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Efectivo</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>04/07</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B8" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D8">
+        <v>36</v>
+      </c>
+      <c r="E8">
+        <v>18000</v>
+      </c>
+      <c r="F8">
+        <v>648000</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D9">
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>18000</v>
+      </c>
+      <c r="F9">
+        <v>432000</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>03/07/2026</v>
+      </c>
+      <c r="B10" t="str">
         <v>Energizante</v>
       </c>
-      <c r="C8">
+      <c r="C10" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D10">
         <v>30</v>
       </c>
-      <c r="D8">
+      <c r="E10">
         <v>2500</v>
       </c>
-      <c r="E8">
+      <c r="F10">
         <v>75000</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>04/07/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>1800</v>
+      </c>
+      <c r="F11">
+        <v>54000</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>04/07/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Agua 2L</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D12">
+        <v>36</v>
+      </c>
+      <c r="E12">
+        <v>900</v>
+      </c>
+      <c r="F12">
+        <v>32400</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>04/07/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Jugo 1L</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D13">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>1100</v>
+      </c>
+      <c r="F13">
+        <v>46200</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>05/07/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D14">
+        <v>36</v>
+      </c>
+      <c r="E14">
+        <v>2200</v>
+      </c>
+      <c r="F14">
+        <v>79200</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>05/07/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Cerveza negra 1L</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D15">
+        <v>42</v>
+      </c>
+      <c r="E15">
+        <v>2600</v>
+      </c>
+      <c r="F15">
+        <v>109200</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>05/07/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Vino tinto</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D16">
+        <v>48</v>
+      </c>
+      <c r="E16">
+        <v>3500</v>
+      </c>
+      <c r="F16">
+        <v>168000</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>05/07/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>3200</v>
+      </c>
+      <c r="F17">
+        <v>19200</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D18">
+        <v>42</v>
+      </c>
+      <c r="E18">
+        <v>3200</v>
+      </c>
+      <c r="F18">
+        <v>134400</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Fernet 750ml</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Aperitivos</v>
+      </c>
+      <c r="D19">
+        <v>48</v>
+      </c>
+      <c r="E19">
+        <v>9500</v>
+      </c>
+      <c r="F19">
+        <v>456000</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>07/07/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D20">
+        <v>48</v>
+      </c>
+      <c r="E20">
+        <v>18000</v>
+      </c>
+      <c r="F20">
+        <v>864000</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>07/07/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Energizante</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>2500</v>
+      </c>
+      <c r="F21">
+        <v>15000</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>07/07/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Soda sifón</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D22">
+        <v>12</v>
+      </c>
+      <c r="E22">
+        <v>1200</v>
+      </c>
+      <c r="F22">
+        <v>14400</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>1800</v>
+      </c>
+      <c r="F23">
+        <v>10800</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Agua 2L</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D24">
+        <v>12</v>
+      </c>
+      <c r="E24">
+        <v>900</v>
+      </c>
+      <c r="F24">
+        <v>10800</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Jugo 1L</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D25">
+        <v>18</v>
+      </c>
+      <c r="E25">
+        <v>1100</v>
+      </c>
+      <c r="F25">
+        <v>19800</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>08/07/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D26">
+        <v>24</v>
+      </c>
+      <c r="E26">
+        <v>2200</v>
+      </c>
+      <c r="F26">
+        <v>52800</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D27">
+        <v>12</v>
+      </c>
+      <c r="E27">
+        <v>2200</v>
+      </c>
+      <c r="F27">
+        <v>26400</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>09/07/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Cerveza negra 1L</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D28">
+        <v>18</v>
+      </c>
+      <c r="E28">
+        <v>2600</v>
+      </c>
+      <c r="F28">
+        <v>46800</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D29">
+        <v>18</v>
+      </c>
+      <c r="E29">
+        <v>3200</v>
+      </c>
+      <c r="F29">
+        <v>57600</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Fernet 750ml</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Aperitivos</v>
+      </c>
+      <c r="D30">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>9500</v>
+      </c>
+      <c r="F30">
+        <v>228000</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>10/07/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Gin 750ml</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>12000</v>
+      </c>
+      <c r="F31">
+        <v>360000</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>11/07/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D32">
+        <v>24</v>
+      </c>
+      <c r="E32">
+        <v>18000</v>
+      </c>
+      <c r="F32">
+        <v>432000</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>11/07/2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Energizante</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D33">
+        <v>30</v>
+      </c>
+      <c r="E33">
+        <v>2500</v>
+      </c>
+      <c r="F33">
+        <v>75000</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>11/07/2026</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Soda sifón</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D34">
+        <v>36</v>
+      </c>
+      <c r="E34">
+        <v>1200</v>
+      </c>
+      <c r="F34">
+        <v>43200</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>11/07/2026</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D35">
+        <v>42</v>
+      </c>
+      <c r="E35">
+        <v>1800</v>
+      </c>
+      <c r="F35">
+        <v>75600</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>12/07/2026</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="E36">
+        <v>1800</v>
+      </c>
+      <c r="F36">
+        <v>54000</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>12/07/2026</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Agua 2L</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D37">
+        <v>36</v>
+      </c>
+      <c r="E37">
+        <v>900</v>
+      </c>
+      <c r="F37">
+        <v>32400</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D38">
+        <v>36</v>
+      </c>
+      <c r="E38">
+        <v>2200</v>
+      </c>
+      <c r="F38">
+        <v>79200</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Cerveza negra 1L</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D39">
+        <v>42</v>
+      </c>
+      <c r="E39">
+        <v>2600</v>
+      </c>
+      <c r="F39">
+        <v>109200</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>13/07/2026</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Vino tinto</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D40">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>3500</v>
+      </c>
+      <c r="F40">
+        <v>168000</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D41">
+        <v>42</v>
+      </c>
+      <c r="E41">
+        <v>3200</v>
+      </c>
+      <c r="F41">
+        <v>134400</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Fernet 750ml</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Aperitivos</v>
+      </c>
+      <c r="D42">
+        <v>48</v>
+      </c>
+      <c r="E42">
+        <v>9500</v>
+      </c>
+      <c r="F42">
+        <v>456000</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Gin 750ml</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43">
+        <v>12000</v>
+      </c>
+      <c r="F43">
+        <v>72000</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>14/07/2026</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D44">
+        <v>12</v>
+      </c>
+      <c r="E44">
+        <v>18000</v>
+      </c>
+      <c r="F44">
+        <v>216000</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D45">
+        <v>48</v>
+      </c>
+      <c r="E45">
+        <v>18000</v>
+      </c>
+      <c r="F45">
+        <v>864000</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>15/07/2026</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Energizante</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>2500</v>
+      </c>
+      <c r="F46">
+        <v>15000</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+      <c r="E47">
+        <v>1800</v>
+      </c>
+      <c r="F47">
+        <v>10800</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Agua 2L</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D48">
+        <v>12</v>
+      </c>
+      <c r="E48">
+        <v>900</v>
+      </c>
+      <c r="F48">
+        <v>10800</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>16/07/2026</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Jugo 1L</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D49">
+        <v>18</v>
+      </c>
+      <c r="E49">
+        <v>1100</v>
+      </c>
+      <c r="F49">
+        <v>19800</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D50">
+        <v>12</v>
+      </c>
+      <c r="E50">
+        <v>2200</v>
+      </c>
+      <c r="F50">
+        <v>26400</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Cerveza negra 1L</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D51">
+        <v>18</v>
+      </c>
+      <c r="E51">
+        <v>2600</v>
+      </c>
+      <c r="F51">
+        <v>46800</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Vino tinto</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D52">
+        <v>24</v>
+      </c>
+      <c r="E52">
+        <v>3500</v>
+      </c>
+      <c r="F52">
+        <v>84000</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>17/07/2026</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D53">
+        <v>30</v>
+      </c>
+      <c r="E53">
+        <v>3200</v>
+      </c>
+      <c r="F53">
+        <v>96000</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>18/07/2026</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D54">
+        <v>18</v>
+      </c>
+      <c r="E54">
+        <v>3200</v>
+      </c>
+      <c r="F54">
+        <v>57600</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>18/07/2026</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Fernet 750ml</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Aperitivos</v>
+      </c>
+      <c r="D55">
+        <v>24</v>
+      </c>
+      <c r="E55">
+        <v>9500</v>
+      </c>
+      <c r="F55">
+        <v>228000</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>19/07/2026</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D56">
+        <v>24</v>
+      </c>
+      <c r="E56">
+        <v>18000</v>
+      </c>
+      <c r="F56">
+        <v>432000</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>19/07/2026</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Energizante</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D57">
+        <v>30</v>
+      </c>
+      <c r="E57">
+        <v>2500</v>
+      </c>
+      <c r="F57">
+        <v>75000</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>19/07/2026</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Soda sifón</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D58">
+        <v>36</v>
+      </c>
+      <c r="E58">
+        <v>1200</v>
+      </c>
+      <c r="F58">
+        <v>43200</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>20/07/2026</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D59">
+        <v>30</v>
+      </c>
+      <c r="E59">
+        <v>1800</v>
+      </c>
+      <c r="F59">
+        <v>54000</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>20/07/2026</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Agua 2L</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D60">
+        <v>36</v>
+      </c>
+      <c r="E60">
+        <v>900</v>
+      </c>
+      <c r="F60">
+        <v>32400</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>20/07/2026</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Jugo 1L</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D61">
+        <v>42</v>
+      </c>
+      <c r="E61">
+        <v>1100</v>
+      </c>
+      <c r="F61">
+        <v>46200</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>20/07/2026</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D62">
+        <v>48</v>
+      </c>
+      <c r="E62">
+        <v>2200</v>
+      </c>
+      <c r="F62">
+        <v>105600</v>
+      </c>
+      <c r="G62" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>21/07/2026</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D63">
+        <v>36</v>
+      </c>
+      <c r="E63">
+        <v>2200</v>
+      </c>
+      <c r="F63">
+        <v>79200</v>
+      </c>
+      <c r="G63" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>21/07/2026</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Cerveza negra 1L</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D64">
+        <v>42</v>
+      </c>
+      <c r="E64">
+        <v>2600</v>
+      </c>
+      <c r="F64">
+        <v>109200</v>
+      </c>
+      <c r="G64" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D65">
+        <v>42</v>
+      </c>
+      <c r="E65">
+        <v>3200</v>
+      </c>
+      <c r="F65">
+        <v>134400</v>
+      </c>
+      <c r="G65" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Fernet 750ml</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Aperitivos</v>
+      </c>
+      <c r="D66">
+        <v>48</v>
+      </c>
+      <c r="E66">
+        <v>9500</v>
+      </c>
+      <c r="F66">
+        <v>456000</v>
+      </c>
+      <c r="G66" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>22/07/2026</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Gin 750ml</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D67">
+        <v>6</v>
+      </c>
+      <c r="E67">
+        <v>12000</v>
+      </c>
+      <c r="F67">
+        <v>72000</v>
+      </c>
+      <c r="G67" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D68">
+        <v>48</v>
+      </c>
+      <c r="E68">
+        <v>18000</v>
+      </c>
+      <c r="F68">
+        <v>864000</v>
+      </c>
+      <c r="G68" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Energizante</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D69">
+        <v>6</v>
+      </c>
+      <c r="E69">
+        <v>2500</v>
+      </c>
+      <c r="F69">
+        <v>15000</v>
+      </c>
+      <c r="G69" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Soda sifón</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D70">
+        <v>12</v>
+      </c>
+      <c r="E70">
+        <v>1200</v>
+      </c>
+      <c r="F70">
+        <v>14400</v>
+      </c>
+      <c r="G70" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>23/07/2026</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D71">
+        <v>18</v>
+      </c>
+      <c r="E71">
+        <v>1800</v>
+      </c>
+      <c r="F71">
+        <v>32400</v>
+      </c>
+      <c r="G71" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>24/07/2026</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+      <c r="E72">
+        <v>1800</v>
+      </c>
+      <c r="F72">
+        <v>10800</v>
+      </c>
+      <c r="G72" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>24/07/2026</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Agua 2L</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D73">
+        <v>12</v>
+      </c>
+      <c r="E73">
+        <v>900</v>
+      </c>
+      <c r="F73">
+        <v>10800</v>
+      </c>
+      <c r="G73" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>25/07/2026</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Cerveza rubia 1L</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D74">
+        <v>12</v>
+      </c>
+      <c r="E74">
+        <v>2200</v>
+      </c>
+      <c r="F74">
+        <v>26400</v>
+      </c>
+      <c r="G74" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>25/07/2026</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Cerveza negra 1L</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Cervezas</v>
+      </c>
+      <c r="D75">
+        <v>18</v>
+      </c>
+      <c r="E75">
+        <v>2600</v>
+      </c>
+      <c r="F75">
+        <v>46800</v>
+      </c>
+      <c r="G75" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>25/07/2026</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Vino tinto</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D76">
+        <v>24</v>
+      </c>
+      <c r="E76">
+        <v>3500</v>
+      </c>
+      <c r="F76">
+        <v>84000</v>
+      </c>
+      <c r="G76" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>26/07/2026</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Vino blanco</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Vinos</v>
+      </c>
+      <c r="D77">
+        <v>18</v>
+      </c>
+      <c r="E77">
+        <v>3200</v>
+      </c>
+      <c r="F77">
+        <v>57600</v>
+      </c>
+      <c r="G77" t="str">
+        <v>Débito</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>26/07/2026</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Fernet 750ml</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Aperitivos</v>
+      </c>
+      <c r="D78">
+        <v>24</v>
+      </c>
+      <c r="E78">
+        <v>9500</v>
+      </c>
+      <c r="F78">
+        <v>228000</v>
+      </c>
+      <c r="G78" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>26/07/2026</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Gin 750ml</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D79">
+        <v>30</v>
+      </c>
+      <c r="E79">
+        <v>12000</v>
+      </c>
+      <c r="F79">
+        <v>360000</v>
+      </c>
+      <c r="G79" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>26/07/2026</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D80">
+        <v>36</v>
+      </c>
+      <c r="E80">
+        <v>18000</v>
+      </c>
+      <c r="F80">
+        <v>648000</v>
+      </c>
+      <c r="G80" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Whisky 750ml</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Destilados</v>
+      </c>
+      <c r="D81">
+        <v>24</v>
+      </c>
+      <c r="E81">
+        <v>18000</v>
+      </c>
+      <c r="F81">
+        <v>432000</v>
+      </c>
+      <c r="G81" t="str">
+        <v>Cuenta corriente</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>27/07/2026</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Energizante</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D82">
+        <v>30</v>
+      </c>
+      <c r="E82">
+        <v>2500</v>
+      </c>
+      <c r="F82">
+        <v>75000</v>
+      </c>
+      <c r="G82" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Gaseosa 2.25L</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D83">
+        <v>30</v>
+      </c>
+      <c r="E83">
+        <v>1800</v>
+      </c>
+      <c r="F83">
+        <v>54000</v>
+      </c>
+      <c r="G83" t="str">
+        <v>Efectivo</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Agua 2L</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D84">
+        <v>36</v>
+      </c>
+      <c r="E84">
+        <v>900</v>
+      </c>
+      <c r="F84">
+        <v>32400</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Transferencia</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Jugo 1L</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Bebidas sin alcohol</v>
+      </c>
+      <c r="D85">
+        <v>42</v>
+      </c>
+      <c r="E85">
+        <v>1100</v>
+      </c>
+      <c r="F85">
+        <v>46200</v>
+      </c>
+      <c r="G85" t="str">
+        <v>Débito</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G85"/>
   </ignoredErrors>
 </worksheet>
 </file>